--- a/Calendar.xlsx
+++ b/Calendar.xlsx
@@ -7,6 +7,7 @@
     <sheet name="오지인터팩코리아" sheetId="2" r:id="rId2"/>
     <sheet name="일신포장산업" sheetId="3" r:id="rId3"/>
     <sheet name="동진물류포장" sheetId="4" r:id="rId4"/>
+    <sheet name="제이에스티" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -35,14 +36,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="7">
-    <numFmt numFmtId="6" formatCode="&quot;₩&quot;#,##0;[Red]\-&quot;₩&quot;#,##0"/>
+  <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
-    <numFmt numFmtId="177" formatCode="&quot;₩&quot;#,##0_);[Red]\(&quot;₩&quot;#,##0\)"/>
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -406,12 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -427,6 +425,9 @@
       <c r="D1" t="str">
         <v>출처</v>
       </c>
+      <c r="E1" t="str">
+        <v>상세JSON</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -441,6 +442,9 @@
       <c r="D2" t="str">
         <v>발주서</v>
       </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -455,6 +459,9 @@
       <c r="D3" t="str">
         <v>발주서</v>
       </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -469,6 +476,9 @@
       <c r="D4" t="str">
         <v>발주서</v>
       </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -483,6 +493,9 @@
       <c r="D5" t="str">
         <v>발주서</v>
       </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -497,6 +510,9 @@
       <c r="D6" t="str">
         <v>발주서</v>
       </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -511,6 +527,9 @@
       <c r="D7" t="str">
         <v>발주서</v>
       </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -525,6 +544,9 @@
       <c r="D8" t="str">
         <v>발주서</v>
       </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -539,22 +561,26 @@
       <c r="D9" t="str">
         <v>발주서</v>
       </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -570,6 +596,9 @@
       <c r="D1" t="str">
         <v>출처</v>
       </c>
+      <c r="E1" t="str">
+        <v>상세JSON</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -584,6 +613,9 @@
       <c r="D2" t="str">
         <v>발주서</v>
       </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -598,6 +630,9 @@
       <c r="D3" t="str">
         <v>발주서</v>
       </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -612,6 +647,9 @@
       <c r="D4" t="str">
         <v>발주서</v>
       </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -626,6 +664,9 @@
       <c r="D5" t="str">
         <v>발주서</v>
       </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -640,6 +681,9 @@
       <c r="D6" t="str">
         <v>발주서</v>
       </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -654,6 +698,9 @@
       <c r="D7" t="str">
         <v>발주서</v>
       </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -668,6 +715,9 @@
       <c r="D8" t="str">
         <v>발주서</v>
       </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -682,6 +732,9 @@
       <c r="D9" t="str">
         <v>발주서</v>
       </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -696,6 +749,9 @@
       <c r="D10" t="str">
         <v>발주서</v>
       </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -710,22 +766,26 @@
       <c r="D11" t="str">
         <v>발주서</v>
       </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -741,6 +801,9 @@
       <c r="D1" t="str">
         <v>출처</v>
       </c>
+      <c r="E1" t="str">
+        <v>상세JSON</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -755,22 +818,26 @@
       <c r="D2" t="str">
         <v>직접 입력</v>
       </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,6 +853,9 @@
       <c r="D1" t="str">
         <v>출처</v>
       </c>
+      <c r="E1" t="str">
+        <v>상세JSON</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -800,6 +870,9 @@
       <c r="D2" t="str">
         <v>직접 입력</v>
       </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -814,10 +887,99 @@
       <c r="D3" t="str">
         <v>직접 입력</v>
       </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E4"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>업체명</v>
+      </c>
+      <c r="B1" t="str">
+        <v>입고일</v>
+      </c>
+      <c r="C1" t="str">
+        <v>완료</v>
+      </c>
+      <c r="D1" t="str">
+        <v>출처</v>
+      </c>
+      <c r="E1" t="str">
+        <v>상세JSON</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>제이에스티</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-08-04</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E2" t="str">
+        <v>[{"sheet":"소모품","partNo":"C18-M5x30","name":"SEMS 렌지볼트 M5*30","qty":2000,"note":""},{"sheet":"소모품","partNo":"C04-M6X15","name":"접시머리 사라렌지M6*15","qty":2000,"note":""},{"sheet":"소모품","partNo":"C04-M6X20","name":"접시머리 사라렌지M6*20","qty":2000,"note":""},{"sheet":"소모품","partNo":"C03-M3X8","name":"접시머리볼트 M3*8","qty":6000,"note":""},{"sheet":"소모품","partNo":"C18-M3x8","name":"둥근SEMS 볼트M3*8","qty":20000,"note":""},{"sheet":"소모품","partNo":"C02-M4x12","name":"PAN HEAD TAP TITE M4X12(둥근머리 탭타이트4*12) 이종컷팅","qty":6000,"note":""},{"sheet":"소모품","partNo":"EP-0004","name":"SHOCK WATCH","qty":150,"note":""},{"sheet":"소모품","partNo":"EP-0003","name":"TIP N TELL","qty":300,"note":""},{"sheet":"소모품","partNo":"","name":"노란색 벨크로테이프 폭5cm","qty":1,"note":""},{"sheet":"소모품","partNo":"","name":"노란색 벨크로테이프 폭2.5cm","qty":1,"note":""},{"sheet":"원자재","partNo":"RA-09S-1476","name":"WATER DROP LEVEL","qty":300,"note":"5개 선납으로 295개 납품예정"},{"sheet":"원자재","partNo":"RA-06S-0214","name":"COUPLING DISK","qty":200,"note":""},{"sheet":"원자재","partNo":"RA-02S-0042","name":"COUPLING DISK","qty":100,"note":""},{"sheet":"원자재","partNo":"RA-02S-2026","name":"COUPLING","qty":50,"note":""},{"sheet":"원자재","partNo":"RA-07S-1668","name":"MICROMTR HEAD (VA)","qty":250,"note":""},{"sheet":"원자재","partNo":"RA-03S-6045","name":"SMPS-RPS-200-24V","qty":200,"note":""},{"sheet":"원자재","partNo":"RA-04S-5179","name":"SMPS-RPS-75-24","qty":100,"note":""},{"sheet":"원자재","partNo":"RP-02S-0014","name":"COLOR FILTER","qty":100,"note":""},{"sheet":"원자재","partNo":"RP-00S-5053","name":"BARRIER ENVELOPES SIZE0","qty":20000,"note":""},{"sheet":"원자재","partNo":"RP-00S-5055","name":"BARRIER ENVELOPES SIZE2","qty":20000,"note":""},{"sheet":"원자재","partNo":"RP-00S-5057","name":"BARRIER ENVELOPES SIZE4","qty":10000,"note":""},{"sheet":"원자재","partNo":"RP-00S-5041","name":"POWER CRD_INTERNATIONAL","qty":80,"note":""},{"sheet":"원자재","partNo":"RD-00S-5204","name":"POWER CRD_US","qty":100,"note":""}]</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>제이에스티</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-08-05</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E3" t="str">
+        <v>[{"sheet":"소모품","partNo":"","name":"PET BAND 1.0T x 19mm x 20kg G/E(코드스랩밴드 신형)","qty":5,"note":""},{"sheet":"소모품","partNo":"","name":"비닐PE (입체가공 신재*1)(0.05*900*1500)","qty":600,"note":""},{"sheet":"원자재","partNo":"RF-01S-5030","name":"AC adapter","qty":37,"note":""}]</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>제이에스티</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-08-18</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>발주서</v>
+      </c>
+      <c r="E4" t="str">
+        <v>[{"sheet":"소모품","partNo":"RA-09A-2728","name":"ASM MAIN BOX BOLT","qty":200,"note":"휴가뒤 납품"},{"sheet":"소모품","partNo":"RA-09A-2727","name":"ASM SCAN CEPH BOLT","qty":200,"note":"휴가뒤 납품"},{"sheet":"원자재","partNo":"RA-02S-0042","name":"COUPLING DISK","qty":50,"note":""},{"sheet":"원자재","partNo":"RA-04S-5179","name":"SMPS-RPS-75-24","qty":100,"note":"휴가뒤 납품"},{"sheet":"원자재","partNo":"RA-7-2","name":"LAN GIGA","qty":100,"note":""},{"sheet":"원자재","partNo":"RA-9-12","name":"SCEPH LAN","qty":150,"note":""},{"sheet":"원자재","partNo":"RA-09A-0345","name":"ASM REMOTE CONTROL","qty":200,"note":"휴가뒤 납품"},{"sheet":"원자재","partNo":"RF-01G-0168","name":"BOT RUBBER","qty":600,"note":"휴가뒤 납품"}]</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Calendar.xlsx
+++ b/Calendar.xlsx
@@ -36,10 +36,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
+  <numFmts count="7">
+    <numFmt numFmtId="6" formatCode="&quot;₩&quot;#,##0;[Red]\-&quot;₩&quot;#,##0"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
+    <numFmt numFmtId="177" formatCode="&quot;₩&quot;#,##0_);[Red]\(&quot;₩&quot;#,##0\)"/>
+    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="1">
     <font>
